--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -526,7 +526,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0</t>
   </si>
   <si>
     <t>Practitioner.meta.security</t>
@@ -694,7 +694,7 @@
     <t>specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-specialty|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-specialty|2.2.0}
 </t>
   </si>
   <si>
@@ -1942,7 +1942,7 @@
     <t>Practitioner.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1990,7 +1990,7 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
@@ -2639,7 +2639,7 @@
     <t>Practitioner.qualification:degree.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.1.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.1.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -2799,7 +2799,7 @@
     <t>Compétence acquise par le professionnel (competence) R39 ou Compétence exclusive exercée par le professionnel à titre exclusif (competenceExclusive) R40 ou Diplôme d'études spécialisées complémentaires (DESC)DESCnonQualifian R42 ou Capacité (savoir-faire)de médecine (capaciteSavoirFaire) R43 ou Qualification de praticien adjoint contractuel (qualificationPAC) R44 ou Fonction qualifiée (Synonyme: fonctionQualifiee) R45 ou Droit d'exercice complémentaire (Synonyme: droitExerciceComplementaire) R97 ou Orientation particulière (Synonyme: orientationParticuliere) G13 ou Activité ponctuelle du professionnel de type expertise (attributionParticuliere) G13.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS|20260730120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS|20260928120000</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.code.text</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
